--- a/artfynd/A 32590-2026 artfynd.xlsx
+++ b/artfynd/A 32590-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -904,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136203169</v>
+        <v>136203177</v>
       </c>
       <c r="B4" t="n">
         <v>58006</v>
@@ -933,24 +933,27 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skaite, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>805827</v>
+        <v>805833</v>
       </c>
       <c r="R4" t="n">
-        <v>7368653</v>
+        <v>7368655</v>
       </c>
       <c r="S4" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,19 +992,19 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Hackmärken från födosök</t>
         </is>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG4" t="b">
         <v>0</v>
@@ -1019,131 +1022,6 @@
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136203169</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>136203177</v>
-      </c>
-      <c r="B5" t="n">
-        <v>58006</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Skaite, Nb</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>805833</v>
-      </c>
-      <c r="R5" t="n">
-        <v>7368655</v>
-      </c>
-      <c r="S5" t="n">
-        <v>5</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Boden</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Råneå</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>19:02</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>19:02</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hackmärken från födosök</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136203177</t>
         </is>
@@ -1154,7 +1032,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32590-2026 artfynd.xlsx
+++ b/artfynd/A 32590-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136203174</v>
       </c>
       <c r="B2" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136203170</v>
       </c>
       <c r="B3" t="n">
-        <v>83461</v>
+        <v>83463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136203177</v>
       </c>
       <c r="B4" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
